--- a/artfynd/A 8266-2022 artfynd.xlsx
+++ b/artfynd/A 8266-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8266-2022 artfynd.xlsx
+++ b/artfynd/A 8266-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>78888146</v>
       </c>
       <c r="B2" t="n">
-        <v>91623</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
